--- a/output/tables/GD/finished tables/Relative_Heterozygosity.xlsx
+++ b/output/tables/GD/finished tables/Relative_Heterozygosity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\R_WD\revised_bison_popgen\output\tables\GD\finished tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_RWD\revised_bison_popgen\output\tables\GD\finished tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A900E68-E68D-4835-826B-671A494C5A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-118" yWindow="-118" windowWidth="20343" windowHeight="12934" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -578,12 +578,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.05" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -597,7 +597,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>22</v>
       </c>
@@ -611,7 +611,7 @@
         <v>0.83399999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="18"/>
       <c r="B3" s="2" t="s">
         <v>17</v>
@@ -623,7 +623,7 @@
         <v>0.64392857142857096</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="3" t="s">
         <v>16</v>
@@ -635,7 +635,7 @@
         <v>0.124615384615385</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="18"/>
       <c r="B5" s="2" t="s">
         <v>13</v>
@@ -647,7 +647,7 @@
         <v>8.3333333333333297E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="3" t="s">
         <v>18</v>
@@ -659,7 +659,7 @@
         <v>2.1250000000000002E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="18"/>
       <c r="B7" s="2" t="s">
         <v>9</v>
@@ -671,7 +671,7 @@
         <v>1.9090909090909099E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="18"/>
       <c r="B8" s="3" t="s">
         <v>15</v>
@@ -683,7 +683,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="18"/>
       <c r="B9" s="2" t="s">
         <v>14</v>
@@ -695,7 +695,7 @@
         <v>4.2857142857142903E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="18"/>
       <c r="B10" s="3" t="s">
         <v>10</v>
@@ -707,7 +707,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="18"/>
       <c r="B11" s="2" t="s">
         <v>8</v>
@@ -719,7 +719,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="18"/>
       <c r="B12" s="3" t="s">
         <v>7</v>
@@ -731,7 +731,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="18"/>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -743,7 +743,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="18"/>
       <c r="B14" s="3" t="s">
         <v>11</v>
@@ -755,7 +755,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="2" t="s">
         <v>4</v>
@@ -767,7 +767,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="19"/>
       <c r="B16" s="4" t="s">
         <v>6</v>
@@ -779,7 +779,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>23</v>
       </c>
@@ -793,7 +793,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="18"/>
       <c r="B18" s="3" t="s">
         <v>17</v>
@@ -805,7 +805,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="18"/>
       <c r="B19" s="2" t="s">
         <v>9</v>
@@ -817,7 +817,7 @@
         <v>0.34517647058823497</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="18"/>
       <c r="B20" s="3" t="s">
         <v>16</v>
@@ -829,7 +829,7 @@
         <v>0.41199999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="18"/>
       <c r="B21" s="2" t="s">
         <v>14</v>
@@ -841,7 +841,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="18"/>
       <c r="B22" s="3" t="s">
         <v>18</v>
@@ -853,7 +853,7 @@
         <v>1.38461538461538E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="18"/>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -865,7 +865,7 @@
         <v>1.63636363636364E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="18"/>
       <c r="B24" s="3" t="s">
         <v>13</v>
@@ -877,7 +877,7 @@
         <v>1.63636363636364E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="18"/>
       <c r="B25" s="2" t="s">
         <v>10</v>
@@ -889,7 +889,7 @@
         <v>1.63636363636364E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="18"/>
       <c r="B26" s="3" t="s">
         <v>19</v>
@@ -901,7 +901,7 @@
         <v>1.63636363636364E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="18"/>
       <c r="B27" s="2" t="s">
         <v>11</v>
@@ -913,7 +913,7 @@
         <v>1.63636363636364E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="18"/>
       <c r="B28" s="3" t="s">
         <v>7</v>
@@ -925,7 +925,7 @@
         <v>1.63636363636364E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="18"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
@@ -937,7 +937,7 @@
         <v>1.63636363636364E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="18"/>
       <c r="B30" s="3" t="s">
         <v>8</v>
@@ -949,7 +949,7 @@
         <v>1.63636363636364E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="18"/>
       <c r="B31" s="2" t="s">
         <v>6</v>
@@ -961,7 +961,7 @@
         <v>1.63636363636364E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="18"/>
       <c r="B32" s="3" t="s">
         <v>5</v>
@@ -973,7 +973,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="18"/>
       <c r="B33" s="2" t="s">
         <v>4</v>
@@ -985,7 +985,7 @@
         <v>1.63636363636364E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="19"/>
       <c r="B34" s="4" t="s">
         <v>21</v>
